--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0002T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0002T0006Z000C1N27_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18.85457518086784</v>
+        <v>18.17233773830152</v>
       </c>
       <c r="D2" t="n">
-        <v>12.64872633025864</v>
+        <v>18.57827985111802</v>
       </c>
       <c r="E2" t="n">
-        <v>5.14311447827411</v>
+        <v>5.275504744591872</v>
       </c>
       <c r="F2" t="n">
-        <v>2.248957336981462</v>
+        <v>4.391568321866687</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>7.214523759548148</v>
+        <v>18.85457518086784</v>
       </c>
       <c r="D3" t="n">
-        <v>7.598734056836814</v>
+        <v>12.64872633025864</v>
       </c>
       <c r="E3" t="n">
-        <v>5.14311447827411</v>
+        <v>5.275504744591872</v>
       </c>
       <c r="F3" t="n">
-        <v>2.248957336981462</v>
+        <v>4.391568321866687</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,23 +544,55 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
+        <v>7.214523759548148</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7.598734056836814</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5.275504744591872</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4.391568321866687</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>T12594</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>W0065F0002T0006Z000C1N27.png</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
         <v>8.861514412049184</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D5" t="n">
         <v>8.217602051261053</v>
       </c>
-      <c r="E4" t="n">
-        <v>5.14311447827411</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2.248957336981462</v>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="E5" t="n">
+        <v>5.275504744591872</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4.391568321866687</v>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>T12594</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0002T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0002T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18.17233773830152</v>
+        <v>2.953004882473997</v>
       </c>
       <c r="D2" t="n">
-        <v>18.57827985111802</v>
+        <v>3.018970475806679</v>
       </c>
       <c r="E2" t="n">
-        <v>5.275504744591872</v>
+        <v>0.8572695209961794</v>
       </c>
       <c r="F2" t="n">
-        <v>4.391568321866687</v>
+        <v>0.7136298523033366</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>18.85457518086784</v>
+        <v>3.063868466891024</v>
       </c>
       <c r="D3" t="n">
-        <v>12.64872633025864</v>
+        <v>2.055418028667029</v>
       </c>
       <c r="E3" t="n">
-        <v>5.275504744591872</v>
+        <v>0.8572695209961794</v>
       </c>
       <c r="F3" t="n">
-        <v>4.391568321866687</v>
+        <v>0.7136298523033366</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>7.214523759548148</v>
+        <v>1.172360110926574</v>
       </c>
       <c r="D4" t="n">
-        <v>7.598734056836814</v>
+        <v>1.234794284235982</v>
       </c>
       <c r="E4" t="n">
-        <v>5.275504744591872</v>
+        <v>0.8572695209961794</v>
       </c>
       <c r="F4" t="n">
-        <v>4.391568321866687</v>
+        <v>0.7136298523033366</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>8.861514412049184</v>
+        <v>1.439996091957992</v>
       </c>
       <c r="D5" t="n">
-        <v>8.217602051261053</v>
+        <v>1.335360333329921</v>
       </c>
       <c r="E5" t="n">
-        <v>5.275504744591872</v>
+        <v>0.8572695209961794</v>
       </c>
       <c r="F5" t="n">
-        <v>4.391568321866687</v>
+        <v>0.7136298523033366</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
